--- a/dev/observations-summary.xlsx
+++ b/dev/observations-summary.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="74">
   <si>
     <t>Profile</t>
   </si>
@@ -114,6 +114,30 @@
   </si>
   <si>
     <t>SNOMED CT#736535009</t>
+  </si>
+  <si>
+    <t>mii-pr-pro-observation-phq-15</t>
+  </si>
+  <si>
+    <t>MII PR PRO Observation PHQ-15</t>
+  </si>
+  <si>
+    <t>LOINC#70273-8</t>
+  </si>
+  <si>
+    <t>LOINC#69728-4</t>
+  </si>
+  <si>
+    <t>mii-pr-pro-observation-phq-9</t>
+  </si>
+  <si>
+    <t>MII PR PRO Observation PHQ-9</t>
+  </si>
+  <si>
+    <t>LOINC#44261-6</t>
+  </si>
+  <si>
+    <t>LOINC#44249-1</t>
   </si>
   <si>
     <t>mii-pr-pro-promis-29-anxiety-tscore</t>
@@ -343,7 +367,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K17"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -588,15 +612,15 @@
         <v>14</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>14</v>
+        <v>37</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C8" t="s" s="2">
         <v>14</v>
@@ -605,7 +629,7 @@
         <v>14</v>
       </c>
       <c r="E8" t="s" s="2">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="F8" t="s" s="2">
         <v>14</v>
@@ -623,15 +647,15 @@
         <v>14</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>14</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C9" t="s" s="2">
         <v>14</v>
@@ -640,7 +664,7 @@
         <v>14</v>
       </c>
       <c r="E9" t="s" s="2">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F9" t="s" s="2">
         <v>14</v>
@@ -663,10 +687,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C10" t="s" s="2">
         <v>14</v>
@@ -675,7 +699,7 @@
         <v>14</v>
       </c>
       <c r="E10" t="s" s="2">
-        <v>44</v>
+        <v>15</v>
       </c>
       <c r="F10" t="s" s="2">
         <v>14</v>
@@ -698,10 +722,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C11" t="s" s="2">
         <v>14</v>
@@ -710,7 +734,7 @@
         <v>14</v>
       </c>
       <c r="E11" t="s" s="2">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F11" t="s" s="2">
         <v>14</v>
@@ -733,10 +757,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C12" t="s" s="2">
         <v>14</v>
@@ -745,7 +769,7 @@
         <v>14</v>
       </c>
       <c r="E12" t="s" s="2">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F12" t="s" s="2">
         <v>14</v>
@@ -768,10 +792,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C13" t="s" s="2">
         <v>14</v>
@@ -780,7 +804,7 @@
         <v>14</v>
       </c>
       <c r="E13" t="s" s="2">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F13" t="s" s="2">
         <v>14</v>
@@ -803,10 +827,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C14" t="s" s="2">
         <v>14</v>
@@ -815,7 +839,7 @@
         <v>14</v>
       </c>
       <c r="E14" t="s" s="2">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F14" t="s" s="2">
         <v>14</v>
@@ -838,10 +862,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C15" t="s" s="2">
         <v>14</v>
@@ -850,7 +874,7 @@
         <v>14</v>
       </c>
       <c r="E15" t="s" s="2">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F15" t="s" s="2">
         <v>14</v>
@@ -873,10 +897,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C16" t="s" s="2">
         <v>14</v>
@@ -885,7 +909,7 @@
         <v>14</v>
       </c>
       <c r="E16" t="s" s="2">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F16" t="s" s="2">
         <v>14</v>
@@ -908,36 +932,106 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C17" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D17" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E17" t="s" s="2">
+        <v>67</v>
+      </c>
+      <c r="F17" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G17" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="H17" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="I17" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J17" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K17" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="B18" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="C18" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D18" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E18" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="F18" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G18" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="H18" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="I18" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J18" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K18" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="B19" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="C19" t="s" s="2">
         <v>13</v>
       </c>
-      <c r="D17" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E17" t="s" s="2">
-        <v>65</v>
-      </c>
-      <c r="F17" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="G17" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="H17" t="s" s="2">
+      <c r="D19" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="F19" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G19" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="H19" t="s" s="2">
         <v>17</v>
       </c>
-      <c r="I17" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="J17" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="K17" t="s" s="2">
+      <c r="I19" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J19" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K19" t="s" s="2">
         <v>14</v>
       </c>
     </row>
